--- a/research/traditional_assets/database/data/kuwait/kuwait_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_reinsurance.xlsx
@@ -588,79 +588,79 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.175</v>
+        <v>0.148</v>
       </c>
       <c r="E2">
-        <v>0.101</v>
+        <v>0.238</v>
       </c>
       <c r="G2">
-        <v>0.1079854809437387</v>
+        <v>0.1139691333597151</v>
       </c>
       <c r="H2">
-        <v>0.1079854809437387</v>
+        <v>0.1139691333597151</v>
       </c>
       <c r="I2">
-        <v>0.1284029038112523</v>
+        <v>0.1254451919271864</v>
       </c>
       <c r="J2">
-        <v>0.1270051000482437</v>
+        <v>0.1241176651388307</v>
       </c>
       <c r="K2">
-        <v>23.4</v>
+        <v>30.5</v>
       </c>
       <c r="L2">
-        <v>0.1061705989110708</v>
+        <v>0.1206964780371983</v>
       </c>
       <c r="M2">
-        <v>3.52</v>
+        <v>4.633</v>
       </c>
       <c r="N2">
-        <v>0.01571428571428572</v>
+        <v>0.01426416256157635</v>
       </c>
       <c r="O2">
-        <v>0.1504273504273504</v>
+        <v>0.1519016393442623</v>
       </c>
       <c r="P2">
-        <v>3.52</v>
+        <v>4.62</v>
       </c>
       <c r="Q2">
-        <v>0.01571428571428572</v>
+        <v>0.01422413793103448</v>
       </c>
       <c r="R2">
-        <v>0.1504273504273504</v>
+        <v>0.1514754098360656</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.0129999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.002805957263112433</v>
       </c>
       <c r="U2">
-        <v>16.2</v>
+        <v>17.9</v>
       </c>
       <c r="V2">
-        <v>0.07232142857142856</v>
+        <v>0.05511083743842364</v>
       </c>
       <c r="W2">
-        <v>0.1151008362026562</v>
+        <v>0.1408125577100647</v>
       </c>
       <c r="X2">
-        <v>0.1168012118467232</v>
+        <v>0.09908455323366638</v>
       </c>
       <c r="Y2">
-        <v>-0.00170037564406704</v>
+        <v>0.04172800447639827</v>
       </c>
       <c r="Z2">
-        <v>1.205030071077091</v>
+        <v>1.260978043912176</v>
       </c>
       <c r="AA2">
-        <v>0.1530449647382882</v>
+        <v>0.1565096506017092</v>
       </c>
       <c r="AB2">
-        <v>0.1168012118467232</v>
+        <v>0.09908455323366638</v>
       </c>
       <c r="AC2">
-        <v>0.03624375289156502</v>
+        <v>0.0574250973680428</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-16.2</v>
+        <v>-17.9</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.07795957651588065</v>
+        <v>-0.05832518735744541</v>
       </c>
       <c r="AK2">
-        <v>-0.08083832335329341</v>
+        <v>-0.07840560665790626</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.5684210526315789</v>
+        <v>-0.561128526645768</v>
       </c>
     </row>
     <row r="3">
@@ -716,79 +716,79 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.175</v>
+        <v>0.148</v>
       </c>
       <c r="E3">
-        <v>0.101</v>
+        <v>0.238</v>
       </c>
       <c r="G3">
-        <v>0.1079854809437387</v>
+        <v>0.1139691333597151</v>
       </c>
       <c r="H3">
-        <v>0.1079854809437387</v>
+        <v>0.1139691333597151</v>
       </c>
       <c r="I3">
-        <v>0.1284029038112523</v>
+        <v>0.1254451919271864</v>
       </c>
       <c r="J3">
-        <v>0.1270051000482437</v>
+        <v>0.1241176651388307</v>
       </c>
       <c r="K3">
-        <v>23.4</v>
+        <v>30.5</v>
       </c>
       <c r="L3">
-        <v>0.1061705989110708</v>
+        <v>0.1206964780371983</v>
       </c>
       <c r="M3">
-        <v>3.52</v>
+        <v>4.633</v>
       </c>
       <c r="N3">
-        <v>0.01571428571428572</v>
+        <v>0.01426416256157635</v>
       </c>
       <c r="O3">
-        <v>0.1504273504273504</v>
+        <v>0.1519016393442623</v>
       </c>
       <c r="P3">
-        <v>3.52</v>
+        <v>4.62</v>
       </c>
       <c r="Q3">
-        <v>0.01571428571428572</v>
+        <v>0.01422413793103448</v>
       </c>
       <c r="R3">
-        <v>0.1504273504273504</v>
+        <v>0.1514754098360656</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.0129999999999999</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.002805957263112433</v>
       </c>
       <c r="U3">
-        <v>16.2</v>
+        <v>17.9</v>
       </c>
       <c r="V3">
-        <v>0.07232142857142856</v>
+        <v>0.05511083743842364</v>
       </c>
       <c r="W3">
-        <v>0.1151008362026562</v>
+        <v>0.1408125577100647</v>
       </c>
       <c r="X3">
-        <v>0.1168012118467232</v>
+        <v>0.09908455323366638</v>
       </c>
       <c r="Y3">
-        <v>-0.00170037564406704</v>
+        <v>0.04172800447639827</v>
       </c>
       <c r="Z3">
-        <v>1.205030071077091</v>
+        <v>1.260978043912176</v>
       </c>
       <c r="AA3">
-        <v>0.1530449647382882</v>
+        <v>0.1565096506017092</v>
       </c>
       <c r="AB3">
-        <v>0.1168012118467232</v>
+        <v>0.09908455323366638</v>
       </c>
       <c r="AC3">
-        <v>0.03624375289156502</v>
+        <v>0.0574250973680428</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-16.2</v>
+        <v>-17.9</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.07795957651588065</v>
+        <v>-0.05832518735744541</v>
       </c>
       <c r="AK3">
-        <v>-0.08083832335329341</v>
+        <v>-0.07840560665790626</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.5684210526315789</v>
+        <v>-0.561128526645768</v>
       </c>
     </row>
   </sheetData>
